--- a/楼盘卖点.xlsx
+++ b/楼盘卖点.xlsx
@@ -970,9 +970,9 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>1、启德跑道区绝对的一线临海地头，超大比例单位直面全无遮挡的维港一线海景。
-2、定位纯正超级豪宅圈层，大户型设计，出入皆是高净值两地名流。
-3、聘请国际顶尖大师团队设计会所与建筑，用料奢华，资产传世属性极强。</t>
+          <t>1、启德跑道区一线临海龙头：超大比例单位直面全无遮挡的维港一线壮阔海景。
+2、纯正顶级高净值圈层：定位纯正超级豪宅圈层，纯大户型设计，出入皆是两地名流。
+3、国际大师团队奢华高定：聘请国际顶尖大师团队设计会所与建筑，用料奢华，传世属性极强。</t>
         </is>
       </c>
     </row>
@@ -2006,9 +2006,9 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>1、香港岛30年唯一新房地铁上盖，自带60 W 平方尺southside大型商业配套，三站就能到中环，楼下就是新加坡国际学校。
-2、单价2.6万起，会德丰和港铁联合开发小区品质极高，拥有独立会所和联合会所。
-3、邻近香港多所顶尖国际学校（如弘立书院、加拿大国际等），极其吸引重视国际教育的家庭。</t>
+          <t>1、港岛30年唯一新房地铁上盖：自带60万呎THE SOUTHSIDE大型商业配套，3站直达中环。
+2、会德丰与港铁联合匠心打造：拥有独立会所和联合会所，交楼精装品质与品牌口碑极高。
+3、紧邻多所顶尖国际名校圈：紧邻新加坡国际学校、弘立书院与加拿大国际学校，教育资源极度雄厚。</t>
         </is>
       </c>
     </row>
@@ -2496,9 +2496,9 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>1、香港岛30年唯一新房地铁上盖，自带60 W 平方尺southside大型商业配套，三站就能到中环，楼下就是新加坡国际学校。
-2、单价2.6万起，会德丰和港铁联合开发小区品质极高，拥有独立会所和联合会所。
-3、邻近香港多所顶尖国际学校（如弘立书院、加拿大国际等），极其吸引重视国际教育的家庭。</t>
+          <t>1、港岛30年唯一新房地铁上盖：自带60万呎THE SOUTHSIDE大型商业配套，3站直达中环。
+2、会德丰与港铁联合匠心打造：拥有独立会所和联合会所，交楼精装品质与品牌口碑极高。
+3、紧邻多所顶尖国际名校圈：紧邻新加坡国际学校、弘立书院与加拿大国际学校，教育资源极度雄厚。</t>
         </is>
       </c>
     </row>

--- a/楼盘卖点.xlsx
+++ b/楼盘卖点.xlsx
@@ -1280,7 +1280,7 @@
         <is>
           <t>1、九龙红磡/土瓜湾大型千伙综合体地标：由恒基兆业、希慎兴业及帝国集团三大财团联袂打造，分4期规划约1,300伙优质住宅，配备约12万平方呎基座商业，重塑九龙核心生活版图。
 2、临近港铁土瓜湾站与开扬维港海景：步行约7-8分钟直达屯马线土瓜湾站，快速接驳港岛东铁线，部分高层单位饱览开扬维多利亚港及启德水岸景致，尽享城市更新红利。
-3、34名校网加持与优质实用户型：坐拥全港顶尖的九龙34名校网，户型主力涵盖两房及三房，开间阔绰实用，高规格交楼标准，为注重子女名校教育及居住品质的家庭首选。</t>
+3、35优质校网加持与优质实用户型：坐拥九龙城35优质小学校网（天神嘉诺撒、马头涌官小等名校）及第一梯队九龙城中学校网，户型主力涵盖两房及三房，开间阔绰实用，为注重子女优质教育及居住品质的家庭首选。</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
         <is>
           <t>1、九龙红磡/土瓜湾大型千伙综合体地标：由恒基兆业、希慎兴业及帝国集团三大财团联袂打造，分4期规划约1,300伙优质住宅，配备约12万平方呎基座商业，重塑九龙核心生活版图。
 2、临近港铁土瓜湾站与开扬维港海景：步行约7-8分钟直达屯马线土瓜湾站，快速接驳港岛东铁线，部分高层单位饱览开扬维多利亚港及启德水岸景致，尽享城市更新红利。
-3、34名校网加持与优质实用户型：坐拥全港顶尖的九龙34名校网，户型主力涵盖两房及三房，开间阔绰实用，高规格交楼标准，为注重子女名校教育及居住品质的家庭首选。</t>
+3、35优质校网加持与优质实用户型：坐拥九龙城35优质小学校网（天神嘉诺撒、马头涌官小等名校）及第一梯队九龙城中学校网，户型主力涵盖两房及三房，开间阔绰实用，为注重子女优质教育及居住品质的家庭首选。</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
         <is>
           <t>1、九龙红磡/土瓜湾大型千伙综合体地标：由恒基兆业、希慎兴业及帝国集团三大财团联袂打造，分4期规划约1,300伙优质住宅，配备约12万平方呎基座商业，重塑九龙核心生活版图。
 2、临近港铁土瓜湾站与开扬维港海景：步行约7-8分钟直达屯马线土瓜湾站，快速接驳港岛东铁线，部分高层单位饱览开扬维多利亚港及启德水岸景致，尽享城市更新红利。
-3、34名校网加持与优质实用户型：坐拥全港顶尖的九龙34名校网，户型主力涵盖两房及三房，开间阔绰实用，高规格交楼标准，为注重子女名校教育及居住品质的家庭首选。</t>
+3、35优质校网加持与优质实用户型：坐拥九龙城35优质小学校网（天神嘉诺撒、马头涌官小等名校）及第一梯队九龙城中学校网，户型主力涵盖两房及三房，开间阔绰实用，为注重子女优质教育及居住品质的家庭首选。</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
         <is>
           <t>1、九龙红磡/土瓜湾大型千伙综合体地标：由恒基兆业、希慎兴业及帝国集团三大财团联袂打造，分4期规划约1,300伙优质住宅，配备约12万平方呎基座商业，重塑九龙核心生活版图。
 2、临近港铁土瓜湾站与开扬维港海景：步行约7-8分钟直达屯马线土瓜湾站，快速接驳港岛东铁线，部分高层单位饱览开扬维多利亚港及启德水岸景致，尽享城市更新红利。
-3、34名校网加持与优质实用户型：坐拥全港顶尖的九龙34名校网，户型主力涵盖两房及三房，开间阔绰实用，高规格交楼标准，为注重子女名校教育及居住品质的家庭首选。</t>
+3、35优质校网加持与优质实用户型：坐拥九龙城35优质小学校网（天神嘉诺撒、马头涌官小等名校）及第一梯队九龙城中学校网，户型主力涵盖两房及三房，开间阔绰实用，为注重子女优质教育及居住品质的家庭首选。</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
         <is>
           <t>1、太子道西核心地脉步入双铁立体枢纽：坐落太子道西102号黄金地段，步行约3-5分钟即达港铁太子站与旺角东站，双轨枢纽极速通达中环金融区及罗湖/落马洲口岸。
 2、都会精品时尚人居高实用智能化空间：现代高雅外立面设计，主力打造高实用率精品都会中小型户型，配备全套国际品牌厨卫家电与智能家居系统，空间灵动高效。
-3、顶尖34名校网与旺角成熟商圈高租金回报：坐拥全港拔尖名校网，下楼即享旺角千亿成熟繁华商业街区，受高薪白领与两地专才热捧，空置率极低且租金回报率突出。</t>
+3、32成熟校网与旺角核心商圈高租金回报：划入油尖旺32公立小学校网，邻近传统名牌学府走廊，下楼即享旺角千亿成熟繁华商业街区，受高薪白领与两地专才热捧，空置率极低且租金回报率突出。</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
         <is>
           <t>1、旺角核心洗衣街地段步入太子及旺角东双铁：坐落洗衣街181号核心地段，步行约3-5分钟直达港铁太子站与旺角东站，畅达全港各核心CBD及高铁西九龙站。
 2、乐风集团高定精装智能化都会精品住宅：现楼交付品质所见即所得，全屋引入德国高端厨卫品牌与全方位智能家居控制系统，户型方正实用，居住质感精致典雅。
-3、顶尖34名校网黄金护城河与高租金回报：坐拥全港第一梯队的九龙34小学名校网与九龙城中学校网，周边生活商圈成熟完备，租客承接力极强，租金收益稳健居高。</t>
+3、32成熟校网与高租金回报：坐拥油尖旺32小学校网，周边生活商圈成熟完备，紧密链接传统名牌学府走廊，租客承接力极强，租金收益稳健居高。</t>
         </is>
       </c>
     </row>
